--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T08:46:48+00:00</t>
+    <t>2024-06-18T10:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,6 +499,22 @@
   </si>
   <si>
     <t>Dispense Request Needed - category.</t>
+  </si>
+  <si>
+    <t>MedicationStatement.extension:visibility-flag</t>
+  </si>
+  <si>
+    <t>visibility-flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/VisibilityFlag}
+</t>
+  </si>
+  <si>
+    <t>Coded preference or assertion about the visibility of the medication line</t>
+  </si>
+  <si>
+    <t>Visibility Flag.</t>
   </si>
   <si>
     <t>MedicationStatement.extension:artifact-version</t>
@@ -1977,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.9921875" customWidth="true" bestFit="true"/>
@@ -3292,7 +3308,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>88</v>
@@ -3373,7 +3389,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>140</v>
@@ -3406,7 +3422,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>88</v>
@@ -3429,9 +3445,7 @@
       <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3509,20 +3523,20 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
@@ -3537,16 +3551,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3605,7 +3619,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>140</v>
@@ -3614,7 +3628,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3625,33 +3639,35 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>171</v>
@@ -3662,9 +3678,7 @@
       <c r="N15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3712,7 +3726,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3721,7 +3735,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>140</v>
@@ -3741,44 +3755,46 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3814,19 +3830,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3838,16 +3854,16 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3855,23 +3871,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>89</v>
@@ -3883,16 +3897,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3930,19 +3944,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3957,13 +3971,13 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3971,12 +3985,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3988,16 +4004,16 @@
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>193</v>
@@ -4005,7 +4021,9 @@
       <c r="M18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4054,28 +4072,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -4083,21 +4101,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4109,17 +4127,15 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4156,37 +4172,37 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4197,46 +4213,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4260,63 +4274,63 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4333,25 +4347,25 @@
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4376,13 +4390,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4400,7 +4414,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4418,21 +4432,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4440,7 +4454,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4455,19 +4469,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4477,10 +4491,10 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>77</v>
@@ -4492,13 +4506,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4516,7 +4530,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4534,21 +4548,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4556,13 +4570,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -4571,18 +4585,20 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4591,10 +4607,10 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>77</v>
@@ -4630,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4648,21 +4664,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4676,7 +4692,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -4685,15 +4701,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4706,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4742,7 +4760,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4760,21 +4778,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4797,17 +4815,15 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4856,7 +4872,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4874,21 +4890,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4899,7 +4915,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4911,18 +4927,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4970,13 +4986,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4985,24 +5001,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5025,17 +5041,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5084,7 +5100,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5099,10 +5115,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5113,10 +5129,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5124,33 +5140,33 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5174,13 +5190,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5198,13 +5214,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -5213,13 +5229,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5227,10 +5243,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5238,31 +5254,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5288,13 +5304,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5312,13 +5328,13 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5327,13 +5343,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5341,10 +5357,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5355,7 +5371,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>89</v>
@@ -5364,18 +5380,20 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5400,13 +5418,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5424,13 +5442,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5439,13 +5457,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5453,10 +5471,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5464,7 +5482,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5479,17 +5497,15 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5514,13 +5530,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5538,10 +5554,10 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5553,13 +5569,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5567,10 +5583,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5593,15 +5609,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5626,13 +5644,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5650,7 +5668,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -5665,24 +5683,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5690,13 +5708,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5705,13 +5723,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5762,10 +5780,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5777,24 +5795,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5802,13 +5820,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5817,17 +5835,15 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5876,7 +5892,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5891,13 +5907,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5905,10 +5921,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5916,7 +5932,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5931,15 +5947,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5988,7 +6006,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6003,13 +6021,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -6017,10 +6035,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6028,7 +6046,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -6040,16 +6058,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6100,7 +6118,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6118,10 +6136,10 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6129,10 +6147,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6140,13 +6158,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -6155,17 +6173,15 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6214,13 +6230,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -6232,10 +6248,10 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6243,10 +6259,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6260,7 +6276,7 @@
         <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -6269,7 +6285,7 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>216</v>
+        <v>352</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>353</v>
@@ -6304,13 +6320,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6328,7 +6344,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6343,13 +6359,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6357,10 +6373,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6383,16 +6399,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>362</v>
+        <v>221</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6418,13 +6434,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6442,7 +6458,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6457,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6471,10 +6487,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6497,15 +6513,17 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6554,7 +6572,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6569,13 +6587,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6583,10 +6601,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6609,17 +6627,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6668,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6683,10 +6699,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>377</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6697,10 +6713,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6711,10 +6727,10 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6723,15 +6739,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>193</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6780,25 +6798,25 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>195</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6809,21 +6827,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6835,17 +6853,15 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6882,37 +6898,37 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6923,26 +6939,24 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -6951,15 +6965,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>204</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6996,19 +7012,19 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7026,7 +7042,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7040,7 +7056,7 @@
         <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>388</v>
@@ -7071,7 +7087,7 @@
         <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>151</v>
+        <v>391</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7122,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7151,46 +7167,44 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7238,7 +7252,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7256,7 +7270,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7274,26 +7288,26 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>398</v>
@@ -7301,9 +7315,11 @@
       <c r="M47" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N47" s="2"/>
+      <c r="N47" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>400</v>
+        <v>179</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7352,39 +7368,39 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>131</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7407,17 +7423,17 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>402</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7466,7 +7482,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7484,21 +7500,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7509,7 +7525,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7521,19 +7537,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7558,13 +7572,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7582,13 +7596,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7600,21 +7614,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7625,7 +7639,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7637,16 +7651,20 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7670,13 +7688,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7700,7 +7718,7 @@
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7712,21 +7730,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7749,7 +7767,7 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>425</v>
@@ -7757,12 +7775,8 @@
       <c r="M51" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7810,7 +7824,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7828,21 +7842,21 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7865,18 +7879,20 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7900,13 +7916,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7924,7 +7940,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7942,21 +7958,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>438</v>
+        <v>337</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7979,20 +7995,18 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>216</v>
+        <v>436</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8016,13 +8030,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8040,7 +8054,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8058,21 +8072,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8095,17 +8109,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8130,13 +8146,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8154,7 +8170,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8172,21 +8188,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8209,19 +8225,17 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8246,13 +8260,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8270,7 +8284,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8288,21 +8302,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8313,7 +8327,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8325,16 +8339,20 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8358,13 +8376,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8382,13 +8400,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8400,21 +8418,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>472</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8425,7 +8443,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8434,16 +8452,16 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>475</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>477</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8494,50 +8512,50 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>195</v>
+        <v>478</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8549,17 +8567,15 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8596,37 +8612,37 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8637,21 +8653,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8660,21 +8676,21 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>216</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>204</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8698,63 +8714,63 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>207</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>484</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8777,19 +8793,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8814,13 +8828,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>486</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8838,7 +8852,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8856,21 +8870,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8893,19 +8907,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8954,7 +8968,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8972,21 +8986,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9009,19 +9023,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9070,7 +9084,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9088,21 +9102,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9125,19 +9139,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9186,7 +9200,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9204,21 +9218,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9241,17 +9255,19 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9300,7 +9316,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9318,17 +9334,131 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN64">
+  <autoFilter ref="A1:AN65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9338,7 +9468,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:21+00:00</t>
+    <t>2024-06-18T10:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:59+00:00</t>
+    <t>2024-06-18T10:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:58:59+00:00</t>
+    <t>2024-06-18T11:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T11:16:13+00:00</t>
+    <t>2024-07-02T10:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(WORK))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T10:09:21+00:00</t>
+    <t>2024-09-06T15:59:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,22 +499,6 @@
   </si>
   <si>
     <t>Dispense Request Needed - category.</t>
-  </si>
-  <si>
-    <t>MedicationStatement.extension:visibility-flag</t>
-  </si>
-  <si>
-    <t>visibility-flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/VisibilityFlag}
-</t>
-  </si>
-  <si>
-    <t>Coded preference or assertion about the visibility of the medication line</t>
-  </si>
-  <si>
-    <t>Visibility Flag.</t>
   </si>
   <si>
     <t>MedicationStatement.extension:artifact-version</t>
@@ -1993,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN65"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.9921875" customWidth="true" bestFit="true"/>
@@ -3308,7 +3292,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>88</v>
@@ -3389,7 +3373,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>140</v>
@@ -3422,7 +3406,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>88</v>
@@ -3445,7 +3429,9 @@
       <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3523,20 +3509,20 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
@@ -3551,16 +3537,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3619,7 +3605,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>140</v>
@@ -3628,7 +3614,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3639,35 +3625,33 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C15" t="s" s="2">
         <v>169</v>
       </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>171</v>
@@ -3678,7 +3662,9 @@
       <c r="N15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="O15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3726,7 +3712,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3735,7 +3721,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>140</v>
@@ -3755,46 +3741,44 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J16" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3830,19 +3814,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3854,16 +3838,16 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3871,21 +3855,23 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="D17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>89</v>
@@ -3897,16 +3883,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3944,19 +3930,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3971,13 +3957,13 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3985,14 +3971,12 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>77</v>
       </c>
@@ -4004,16 +3988,16 @@
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>193</v>
@@ -4021,9 +4005,7 @@
       <c r="M18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>185</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4072,28 +4054,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -4101,21 +4083,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4127,15 +4109,17 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4172,37 +4156,37 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4213,44 +4197,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4274,63 +4260,63 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4347,25 +4333,25 @@
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4390,13 +4376,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4414,7 +4400,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4432,21 +4418,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>131</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4454,7 +4440,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4469,19 +4455,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4491,10 +4477,10 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>77</v>
@@ -4506,13 +4492,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4530,7 +4516,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4548,21 +4534,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4570,13 +4556,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -4585,20 +4571,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4607,10 +4591,10 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>77</v>
@@ -4646,7 +4630,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4664,21 +4648,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4692,7 +4676,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -4701,17 +4685,15 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4724,7 +4706,7 @@
         <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4760,7 +4742,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4778,21 +4760,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4815,15 +4797,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4872,7 +4856,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4890,21 +4874,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4915,7 +4899,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4927,18 +4911,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4986,13 +4970,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -5001,24 +4985,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5041,17 +5025,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5100,7 +5084,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5115,10 +5099,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5129,10 +5113,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5140,33 +5124,33 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
         <v>279</v>
       </c>
+      <c r="N28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5190,13 +5174,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5214,13 +5198,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -5229,13 +5213,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5243,10 +5227,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5254,31 +5238,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5304,37 +5288,37 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AG29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5343,13 +5327,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5357,10 +5341,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5371,7 +5355,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>89</v>
@@ -5380,20 +5364,18 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5418,37 +5400,37 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Y30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5457,13 +5439,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5471,10 +5453,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5482,7 +5464,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5497,15 +5479,17 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5530,13 +5514,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>112</v>
+        <v>290</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5554,10 +5538,10 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5569,13 +5553,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5583,10 +5567,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5609,17 +5593,15 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5644,31 +5626,31 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -5683,24 +5665,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5708,13 +5690,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5723,13 +5705,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5780,10 +5762,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5795,24 +5777,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5820,13 +5802,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5835,15 +5817,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5892,7 +5876,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5907,13 +5891,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5921,10 +5905,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5932,7 +5916,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5947,17 +5931,15 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6006,7 +5988,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6021,13 +6003,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -6035,10 +6017,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6046,7 +6028,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -6058,16 +6040,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6118,7 +6100,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6136,10 +6118,10 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6147,10 +6129,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6158,13 +6140,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -6173,15 +6155,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6230,13 +6214,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -6248,10 +6232,10 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6259,10 +6243,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6276,7 +6260,7 @@
         <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -6285,7 +6269,7 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>352</v>
+        <v>216</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>353</v>
@@ -6320,13 +6304,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6344,7 +6328,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6359,13 +6343,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6373,10 +6357,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6399,16 +6383,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>221</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6434,31 +6418,31 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6473,13 +6457,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6487,10 +6471,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6513,17 +6497,15 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6572,7 +6554,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6587,13 +6569,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6601,10 +6583,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6627,15 +6609,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6684,7 +6668,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6699,10 +6683,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6713,10 +6697,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6727,10 +6711,10 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6739,17 +6723,15 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>380</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>381</v>
+        <v>193</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6798,25 +6780,25 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>379</v>
+        <v>195</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>384</v>
+        <v>196</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6827,21 +6809,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6853,15 +6835,17 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6898,37 +6882,37 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6939,24 +6923,26 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -6965,17 +6951,15 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -7012,19 +6996,19 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7042,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7056,7 +7040,7 @@
         <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>388</v>
@@ -7087,7 +7071,7 @@
         <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>151</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7138,7 +7122,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7167,44 +7151,46 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="N46" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7252,7 +7238,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>395</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7270,7 +7256,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7288,26 +7274,26 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>397</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>398</v>
@@ -7315,11 +7301,9 @@
       <c r="M47" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>179</v>
+        <v>400</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7368,39 +7352,39 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>131</v>
+        <v>402</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>77</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7423,17 +7407,17 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>402</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7482,7 +7466,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7500,21 +7484,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7525,7 +7509,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7537,17 +7521,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7572,13 +7558,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7596,13 +7582,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7614,21 +7600,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7639,7 +7625,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7651,20 +7637,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7688,13 +7670,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>421</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7718,7 +7700,7 @@
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7730,21 +7712,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7767,7 +7749,7 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>197</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>425</v>
@@ -7775,8 +7757,12 @@
       <c r="M51" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7824,7 +7810,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7842,21 +7828,21 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>423</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7879,20 +7865,18 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7916,13 +7900,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7940,7 +7924,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7958,21 +7942,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>337</v>
+        <v>438</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7995,18 +7979,20 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>436</v>
+        <v>216</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8030,13 +8016,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8054,7 +8040,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8072,21 +8058,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8109,19 +8095,17 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8146,13 +8130,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8170,7 +8154,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8188,21 +8172,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8225,17 +8209,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8260,13 +8246,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8284,7 +8270,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8302,21 +8288,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8327,7 +8313,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8339,20 +8325,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>221</v>
+        <v>470</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8376,13 +8358,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>470</v>
+        <v>77</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8400,13 +8382,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8418,21 +8400,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>472</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8443,7 +8425,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8452,16 +8434,16 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>475</v>
+        <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>193</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>194</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8512,50 +8494,50 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>478</v>
+        <v>195</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8567,15 +8549,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8612,37 +8596,37 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8653,21 +8637,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8676,21 +8660,21 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>204</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8714,63 +8698,63 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>77</v>
+        <v>482</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>207</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8793,17 +8777,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>221</v>
+        <v>486</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8828,13 +8814,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>487</v>
+        <v>77</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8852,7 +8838,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8870,21 +8856,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8907,19 +8893,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8968,7 +8954,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8986,21 +8972,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9023,19 +9009,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9084,7 +9070,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9102,21 +9088,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9139,19 +9125,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9200,7 +9186,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9218,21 +9204,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>515</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9255,19 +9241,17 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9316,7 +9300,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9334,131 +9318,17 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN65" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN65">
+  <autoFilter ref="A1:AN64">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9468,7 +9338,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2383" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T15:59:56+00:00</t>
+    <t>2024-09-06T16:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,6 +499,22 @@
   </si>
   <si>
     <t>Dispense Request Needed - category.</t>
+  </si>
+  <si>
+    <t>MedicationStatement.extension:visibility-flag</t>
+  </si>
+  <si>
+    <t>visibility-flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/VisibilityFlag}
+</t>
+  </si>
+  <si>
+    <t>Coded preference or assertion about the visibility of the medication line</t>
+  </si>
+  <si>
+    <t>Visibility Flag.</t>
   </si>
   <si>
     <t>MedicationStatement.extension:artifact-version</t>
@@ -1977,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.9921875" customWidth="true" bestFit="true"/>
@@ -3292,7 +3308,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>88</v>
@@ -3373,7 +3389,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>140</v>
@@ -3406,7 +3422,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>88</v>
@@ -3429,9 +3445,7 @@
       <c r="M13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3509,20 +3523,20 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>132</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
@@ -3537,16 +3551,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3605,7 +3619,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>140</v>
@@ -3614,7 +3628,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3625,33 +3639,35 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>171</v>
@@ -3662,9 +3678,7 @@
       <c r="N15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3712,7 +3726,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3721,7 +3735,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>140</v>
@@ -3741,44 +3755,46 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3814,19 +3830,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3838,16 +3854,16 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3855,23 +3871,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>89</v>
@@ -3883,16 +3897,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3930,19 +3944,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3957,13 +3971,13 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3971,12 +3985,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3988,16 +4004,16 @@
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>193</v>
@@ -4005,7 +4021,9 @@
       <c r="M18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4054,28 +4072,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -4083,21 +4101,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -4109,17 +4127,15 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4156,37 +4172,37 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4197,46 +4213,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4260,63 +4274,63 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4333,25 +4347,25 @@
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4376,13 +4390,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4400,7 +4414,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4418,21 +4432,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4440,7 +4454,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4455,19 +4469,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4477,10 +4491,10 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>77</v>
@@ -4492,13 +4506,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4516,7 +4530,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4534,21 +4548,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4556,13 +4570,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -4571,18 +4585,20 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4591,10 +4607,10 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>77</v>
@@ -4630,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4648,21 +4664,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4676,7 +4692,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -4685,15 +4701,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4706,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4742,7 +4760,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4760,21 +4778,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4797,17 +4815,15 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4856,7 +4872,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4874,21 +4890,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4899,7 +4915,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4911,18 +4927,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4970,13 +4986,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4985,24 +5001,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5025,17 +5041,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5084,7 +5100,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5099,10 +5115,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5113,10 +5129,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5124,33 +5140,33 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5174,13 +5190,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5198,13 +5214,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -5213,13 +5229,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -5227,10 +5243,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5238,31 +5254,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5288,13 +5304,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5312,13 +5328,13 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5327,13 +5343,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5341,10 +5357,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5355,7 +5371,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>89</v>
@@ -5364,18 +5380,20 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5400,13 +5418,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5424,13 +5442,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5439,13 +5457,13 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5453,10 +5471,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5464,7 +5482,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5479,17 +5497,15 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5514,13 +5530,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5538,10 +5554,10 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>88</v>
@@ -5553,13 +5569,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5567,10 +5583,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5593,15 +5609,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5626,13 +5644,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5650,7 +5668,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -5665,24 +5683,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5690,13 +5708,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5705,13 +5723,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5762,10 +5780,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5777,24 +5795,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5802,13 +5820,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5817,17 +5835,15 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5876,7 +5892,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5891,13 +5907,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5905,10 +5921,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5916,7 +5932,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5931,15 +5947,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5988,7 +6006,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6003,13 +6021,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -6017,10 +6035,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6028,7 +6046,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -6040,16 +6058,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6100,7 +6118,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6118,10 +6136,10 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6129,10 +6147,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6140,13 +6158,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -6155,17 +6173,15 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6214,13 +6230,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -6232,10 +6248,10 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6243,10 +6259,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6260,7 +6276,7 @@
         <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -6269,7 +6285,7 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>216</v>
+        <v>352</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>353</v>
@@ -6304,13 +6320,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6328,7 +6344,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6343,13 +6359,13 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6357,10 +6373,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6383,16 +6399,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>362</v>
+        <v>221</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6418,13 +6434,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6442,7 +6458,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6457,13 +6473,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6471,10 +6487,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6497,15 +6513,17 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6554,7 +6572,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6569,13 +6587,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6583,10 +6601,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6609,17 +6627,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6668,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6683,10 +6699,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>377</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6697,10 +6713,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6711,10 +6727,10 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6723,15 +6739,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>193</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6780,25 +6798,25 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>195</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6809,21 +6827,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6835,17 +6853,15 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6882,37 +6898,37 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6923,26 +6939,24 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -6951,15 +6965,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>204</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6996,19 +7012,19 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7026,7 +7042,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7040,7 +7056,7 @@
         <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>388</v>
@@ -7071,7 +7087,7 @@
         <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>151</v>
+        <v>391</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7122,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7151,46 +7167,44 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7238,7 +7252,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>207</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7256,7 +7270,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7274,26 +7288,26 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>397</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>398</v>
@@ -7301,9 +7315,11 @@
       <c r="M47" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N47" s="2"/>
+      <c r="N47" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>400</v>
+        <v>179</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7352,39 +7368,39 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>131</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7407,17 +7423,17 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>402</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7466,7 +7482,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7484,21 +7500,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7509,7 +7525,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7521,19 +7537,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7558,13 +7572,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7582,13 +7596,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7600,21 +7614,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7625,7 +7639,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7637,16 +7651,20 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7670,13 +7688,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7700,7 +7718,7 @@
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7712,21 +7730,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7749,7 +7767,7 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>197</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>425</v>
@@ -7757,12 +7775,8 @@
       <c r="M51" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7810,7 +7824,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7828,21 +7842,21 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7865,18 +7879,20 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7900,13 +7916,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7924,7 +7940,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7942,21 +7958,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>438</v>
+        <v>337</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7979,20 +7995,18 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>216</v>
+        <v>436</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8016,13 +8030,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8040,7 +8054,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8058,21 +8072,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8095,17 +8109,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8130,13 +8146,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8154,7 +8170,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8172,21 +8188,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8209,19 +8225,17 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8246,13 +8260,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8270,7 +8284,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8288,21 +8302,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8313,7 +8327,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8325,16 +8339,20 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8358,13 +8376,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8382,13 +8400,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8400,21 +8418,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>472</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8425,7 +8443,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8434,16 +8452,16 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>475</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
+        <v>477</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8494,50 +8512,50 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>195</v>
+        <v>478</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8549,17 +8567,15 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8596,37 +8612,37 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8637,21 +8653,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8660,21 +8676,21 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>216</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>204</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8698,63 +8714,63 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>207</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>484</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8777,19 +8793,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8814,13 +8828,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>486</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8838,7 +8852,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8856,21 +8870,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8893,19 +8907,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8954,7 +8968,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8972,21 +8986,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9009,19 +9023,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9070,7 +9084,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9088,21 +9102,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9125,19 +9139,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9186,7 +9200,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9204,21 +9218,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9241,17 +9255,19 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9300,7 +9316,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9318,17 +9334,131 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN64">
+  <autoFilter ref="A1:AN65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9338,7 +9468,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-BEMedicationLine.xlsx
+++ b/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T16:05:52+00:00</t>
+    <t>2024-10-22T10:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
